--- a/계산모델_엑셀/파라미터_계산기.xlsx
+++ b/계산모델_엑셀/파라미터_계산기.xlsx
@@ -57,7 +57,7 @@
       <color rgb="00C00000"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -79,6 +79,16 @@
         <fgColor rgb="00D9E1F2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DDEBF7"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="11">
     <border>
@@ -199,7 +209,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -224,6 +234,33 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -589,17 +626,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:E25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
-    <col width="54" customWidth="1" min="4" max="4"/>
+    <col width="6" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>X-ray Void 검사 파라미터 계산기</t>
         </is>
@@ -608,20 +645,22 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>노란칸=입력, 파란칸=자동계산. 값 바꾸면 자동 갱신.</t>
-        </is>
-      </c>
-    </row>
+          <t>노란칸=직접 입력, 파란칸=자동계산. 입력을 바꾸면 자동으로 갱신됩니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="22" t="inlineStr">
         <is>
           <t>■ 입력</t>
         </is>
       </c>
-      <c r="B4" s="3" t="n"/>
-      <c r="C4" s="3" t="n"/>
-      <c r="D4" s="3" t="n"/>
-    </row>
+      <c r="B4" s="23" t="n"/>
+      <c r="C4" s="23" t="n"/>
+      <c r="D4" s="23" t="n"/>
+    </row>
+    <row r="5"/>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
@@ -636,269 +675,253 @@
           <t>µm</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t>검사 대상 범프 nominal 직경(도면/이미지명)</t>
+      <c r="D6" s="24" t="inlineStr">
+        <is>
+          <t>검사 대상 범프의 도면 직경(after reflow)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>void 면적 임계 p</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="n">
-        <v>8</v>
-      </c>
+          <t>범프 높이 h</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n"/>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="D7" s="7" t="inlineStr">
-        <is>
-          <t>합/불 기준 void 면적 비율</t>
+          <t>µm</t>
+        </is>
+      </c>
+      <c r="D7" s="24" t="inlineStr">
+        <is>
+          <t>(알면 입력) kV·W는 직경보다 '높이·적층'이 좌우. 두꺼울수록 W 최적화가 필요</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>허용 void% 상대오차 ε</t>
+          <t>void 면적 임계 p</t>
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="C8" s="6" t="inlineStr"/>
-      <c r="D8" s="7" t="inlineStr">
-        <is>
-          <t>0.10=±10%. 작을수록 N↑(정밀)</t>
+        <v>8</v>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D8" s="24" t="inlineStr">
+        <is>
+          <t>합/불 기준이 되는 void 면적 비율(고객 spec)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>[보정] 기준 범프 d0</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
+          <t>허용 void% 상대오차 ε</t>
+        </is>
+      </c>
+      <c r="B9" s="25" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C9" s="6" t="n"/>
+      <c r="D9" s="24" t="inlineStr">
+        <is>
+          <t>0.10 = ±10%. 작을수록 N이 커짐(더 정밀·더 느림)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="n"/>
+      <c r="B10" s="6" t="n"/>
+      <c r="C10" s="6" t="n"/>
+      <c r="D10" s="7" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="22" t="inlineStr">
+        <is>
+          <t>■ 출력 (자동계산)</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n"/>
+      <c r="C11" s="6" t="n"/>
+      <c r="D11" s="7" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>N (void당 최소 픽셀)</t>
+        </is>
+      </c>
+      <c r="B12" s="26">
+        <f>ROUND(2/B9,0)</f>
+        <v/>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>px</t>
+        </is>
+      </c>
+      <c r="D12" s="27" t="inlineStr">
+        <is>
+          <t>N≈2/ε. void 면적을 픽셀로 쪼갤 때 생기는 오차 기준. 단순 검출만이면 ~5</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>임계 void 지름</t>
+        </is>
+      </c>
+      <c r="B13" s="28">
+        <f>ROUND(B6*SQRT(B8/100),1)</f>
+        <v/>
+      </c>
+      <c r="C13" t="inlineStr">
         <is>
           <t>µm</t>
         </is>
       </c>
-      <c r="D9" s="7" t="inlineStr">
-        <is>
-          <t>★같은 재질의 잘 되는 점. TB500M=26µm→60kV</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>[보정] 기준 kV V0</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="n">
-        <v>26</v>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>kV</t>
-        </is>
-      </c>
-      <c r="D10" s="7" t="inlineStr">
-        <is>
-          <t>기준점 최적 kV</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>[보정] 지수 n</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="n">
-        <v>60</v>
-      </c>
-      <c r="C11" s="6" t="inlineStr"/>
-      <c r="D11" s="7" t="inlineStr">
-        <is>
-          <t>2.5~3.5, 기본3. 'kV보정'시트서 fit</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="B12" s="5" t="n">
-        <v>3</v>
+      <c r="D13" s="27" t="inlineStr">
+        <is>
+          <t>d_void = D·√p. 이 크기를 N픽셀로 담는 것이 R의 기준</t>
+        </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>■ 출력 (자동계산)</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="n"/>
-      <c r="C14" s="3" t="n"/>
-      <c r="D14" s="3" t="n"/>
+      <c r="A14" s="23" t="inlineStr">
+        <is>
+          <t>R_max (권장 최대 해상도)</t>
+        </is>
+      </c>
+      <c r="B14" s="29">
+        <f>ROUND(B6*SQRT(B8/100)/B12,2)</f>
+        <v/>
+      </c>
+      <c r="C14" s="23" t="inlineStr">
+        <is>
+          <t>µm/px</t>
+        </is>
+      </c>
+      <c r="D14" s="30" t="inlineStr">
+        <is>
+          <t>R = D·√p / N. 이 값 이하로 설정(작을수록 정밀하지만 시간 ∝ 1/R²)</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>N (void당 최소 픽셀)</t>
-        </is>
-      </c>
-      <c r="B15" s="8">
-        <f>ROUND(2/B8,0)</f>
+          <t>kV 시작값</t>
+        </is>
+      </c>
+      <c r="B15" s="26">
+        <f>IF(B6&lt;=53,57.5,IF(B6&gt;=119,60.5,60))</f>
         <v/>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>px</t>
-        </is>
-      </c>
-      <c r="D15" s="7" t="inlineStr">
-        <is>
-          <t>N≈2/ε (면적 이산화오차). 검출만이면 ~5</t>
+          <t>kV</t>
+        </is>
+      </c>
+      <c r="D15" s="24" t="inlineStr">
+        <is>
+          <t>크기 영향은 매우 약함(7배 커져도 ~3kV 이동). 시작값일 뿐 — 아래 트림으로 확정</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>R_max (권장 최대 해상도)</t>
-        </is>
-      </c>
-      <c r="B16" s="9">
-        <f>ROUND(B6*SQRT(B7/100)/B15,2)</f>
-        <v/>
+          <t>Power W 시작값</t>
+        </is>
+      </c>
+      <c r="B16" s="31" t="n">
+        <v>4</v>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>µm/px</t>
-        </is>
-      </c>
-      <c r="D16" s="7" t="inlineStr">
-        <is>
-          <t>R=D·√p/N. 이 값 이하 설정(작을수록 정밀·느림)</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="D16" s="24" t="inlineStr">
+        <is>
+          <t>얇은 범프는 4W로 충분. 범프가 두꺼우면(높이 큼) PhaseW 실험으로 최적 W를 확정 — 고정값 아님</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>kV 첫 추정</t>
-        </is>
-      </c>
-      <c r="B17" s="10">
-        <f>ROUND(B11*(B6/B10)^(1/B12),1)</f>
-        <v/>
-      </c>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t>kV</t>
-        </is>
-      </c>
-      <c r="D17" s="7" t="inlineStr">
-        <is>
-          <t>V0·(D/d0)^(1/n). 같은재질 기준점일 때만 유효</t>
+          <t>Frame Average</t>
+        </is>
+      </c>
+      <c r="B17" s="32" t="inlineStr">
+        <is>
+          <t>품질 하한 최소값</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n"/>
+      <c r="D17" s="24" t="inlineStr">
+        <is>
+          <t>반복(재현성)이 허용되는 최소 F. 어두우면 ↑ (64→32 = 시간 절반)</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>Power</t>
-        </is>
-      </c>
-      <c r="B18" s="8" t="inlineStr">
-        <is>
-          <t>≈4 (고정)</t>
-        </is>
-      </c>
-      <c r="C18" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="D18" s="7" t="inlineStr">
-        <is>
-          <t>침투 아님=속도/선속 보조. 계산변수 아님</t>
-        </is>
-      </c>
+      <c r="A18" s="4" t="n"/>
+      <c r="B18" s="6" t="n"/>
+      <c r="C18" s="6" t="n"/>
+      <c r="D18" s="7" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>Frame Average</t>
-        </is>
-      </c>
-      <c r="B19" s="8" t="inlineStr">
-        <is>
-          <t>품질하한 최소값</t>
-        </is>
-      </c>
-      <c r="C19" s="6" t="inlineStr"/>
-      <c r="D19" s="7" t="inlineStr">
-        <is>
-          <t>SNR knob. 어두우면↑ (64→32=시간 절반)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>참고: 임계 void 지름</t>
-        </is>
-      </c>
-      <c r="B21" s="10">
-        <f>ROUND(B6*SQRT(B7/100),1)</f>
-        <v/>
-      </c>
-      <c r="C21" s="6" t="inlineStr">
-        <is>
-          <t>µm</t>
-        </is>
-      </c>
-      <c r="D21" s="7" t="inlineStr">
-        <is>
-          <t>d_void=D·√p (이걸 N픽셀로 담는 게 R 기준)</t>
-        </is>
-      </c>
-    </row>
+      <c r="A19" s="22" t="inlineStr">
+        <is>
+          <t>■ kV 확정 규칙 (가장 중요)</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="n"/>
+      <c r="C19" s="6" t="n"/>
+      <c r="D19" s="7" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="27" t="inlineStr">
+        <is>
+          <t>위 kV 시작값에서 1회 검사 → 측정직경/도면이 97~103% 될 때까지 1kV씩 미세조정(트림). 작게 측정되면 kV를 내리고, 크게 측정되면 kV를 올린다. 검사 가능 창은 ±2.5kV로 좁아 벗어나면 매칭 자체가 실패한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21"/>
+    <row r="22"/>
     <row r="23">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>■ kV 확정 규칙</t>
-        </is>
-      </c>
-      <c r="B23" s="3" t="n"/>
-      <c r="C23" s="3" t="n"/>
-      <c r="D23" s="3" t="n"/>
+      <c r="A23" s="23" t="n"/>
+      <c r="B23" s="23" t="n"/>
+      <c r="C23" s="23" t="n"/>
+      <c r="D23" s="23" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="11" t="inlineStr">
-        <is>
-          <t>위 kV 첫추정에서 시작 → 측정 범프직경이 D의 97~103%가 되고 모든 die가 매칭될 때까지 kV를 1kV씩 미세조정. (재질 다르면 첫추정은 참고만)</t>
-        </is>
-      </c>
-      <c r="B24" s="12" t="n"/>
-      <c r="C24" s="12" t="n"/>
-      <c r="D24" s="13" t="n"/>
+      <c r="A24" s="33" t="inlineStr">
+        <is>
+          <t>■ Power(W) 규칙</t>
+        </is>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" s="14" t="n"/>
-      <c r="B25" s="15" t="n"/>
-      <c r="C25" s="15" t="n"/>
-      <c r="D25" s="16" t="n"/>
+      <c r="A25" s="27" t="inlineStr">
+        <is>
+          <t>W는 광자가 부족한 '두꺼운 범프 내부'의 노이즈를 줄이는 변수. 얇은 범프(26µm)는 둔감→4W. 두꺼운 범프(158µm)는 PhaseW로 최적 W를 찾는다(고정 아님). 직경 문제는 W가 아니라 kV로 고친다.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A24:D25"/>
+  <mergeCells count="2">
+    <mergeCell ref="A20:E22"/>
+    <mergeCell ref="A25:E25"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -913,123 +936,141 @@
   <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="4" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>kV 보정 — 실험점으로 지수 n 자동 fit</t>
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>kV 정하는 법 — 크기 의존은 약하고, 마지막은 트림으로 맞춘다</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>같은 재질에서 '측정직경=nominal 되는' (범프크기, 최적kV) 점을 2개↑ 입력. 아래는 예시(가상).</t>
-        </is>
-      </c>
-    </row>
+      <c r="A2" s="34" t="inlineStr">
+        <is>
+          <t>핵심: 범프 크기가 7배 달라져도 최적 kV는 약 3kV만 이동한다(거의 평평). 예전의 'kV = a·직경^(1/3)' 멱법칙은 실측과 배치되어 폐기함.</t>
+        </is>
+      </c>
+      <c r="B2" s="20" t="n"/>
+      <c r="C2" s="20" t="n"/>
+      <c r="D2" s="20" t="n"/>
+      <c r="E2" s="21" t="n"/>
+    </row>
+    <row r="3"/>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>범프크기 d(µm)</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>최적 kV</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>결과</t>
-        </is>
-      </c>
-      <c r="E4" s="17" t="n"/>
+      <c r="A4" s="22" t="inlineStr">
+        <is>
+          <t>실측 기준점 (같은 재질/유사 적층)</t>
+        </is>
+      </c>
+      <c r="B4" s="23" t="n"/>
+      <c r="D4" s="23" t="n"/>
+      <c r="E4" s="6" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="n">
-        <v>30</v>
-      </c>
-      <c r="B5" s="5" t="n">
-        <v>58</v>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>기울기 (1/n)</t>
-        </is>
-      </c>
-      <c r="E5" s="18">
-        <f>IFERROR(SLOPE(LN(B5:B10),LN(A5:A10)),"점2개↑ 필요")</f>
-        <v/>
-      </c>
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>범프 크기</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>측정 결과</t>
+        </is>
+      </c>
+      <c r="C5" s="35" t="inlineStr">
+        <is>
+          <t>최적 kV(추정)</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="n"/>
+      <c r="E5" s="36" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="n">
-        <v>120</v>
-      </c>
-      <c r="B6" s="5" t="n">
-        <v>92</v>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>fit된 n</t>
-        </is>
-      </c>
-      <c r="E6" s="9">
-        <f>IFERROR(1/E5,"-")</f>
-        <v/>
-      </c>
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>26µm(TB500M)</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>60kV에서 Q=92% → 더 내려야</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>≈ 57~58</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="n"/>
+      <c r="E6" s="37" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="n"/>
-      <c r="B7" s="5" t="n"/>
-      <c r="D7" s="19" t="inlineStr">
-        <is>
-          <t>→ 계산기 'n'칸에 입력</t>
-        </is>
-      </c>
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>80µm(NXP)</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>60kV에서 Q=100%</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>60.0</t>
+        </is>
+      </c>
+      <c r="D7" s="19" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="n"/>
-      <c r="B8" s="5" t="n"/>
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>182µm급</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>60kV에서 Q=102% → 살짝 올려</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>≈ 60.5~61</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="n"/>
-      <c r="B9" s="5" t="n"/>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>예측: 25µm의 kV</t>
-        </is>
-      </c>
-      <c r="E9" s="10">
-        <f>IFERROR(EXP(INTERCEPT(LN(B5:B10),LN(A5:A10)))*25^E5,"-")</f>
-        <v/>
-      </c>
+      <c r="A9" s="6" t="n"/>
+      <c r="B9" s="6" t="n"/>
+      <c r="D9" s="4" t="n"/>
+      <c r="E9" s="38" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="n"/>
-      <c r="B10" s="5" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>원리: V=a·d^(1/n) → lnV=ln a+(1/n)·ln d. 기울기=1/n. 재질 바뀌면 다시 fit.</t>
-        </is>
-      </c>
-      <c r="B12" s="20" t="n"/>
-      <c r="C12" s="20" t="n"/>
-      <c r="D12" s="20" t="n"/>
-      <c r="E12" s="21" t="n"/>
-    </row>
+      <c r="A10" s="22" t="inlineStr">
+        <is>
+          <t>확정 절차</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="27" t="inlineStr">
+        <is>
+          <t>① 크기대별 시작 kV로 1회 검사 → ② 측정직경/도면이 97~103% 될 때까지 1kV씩 조정(작으면 kV↓, 크면 kV↑) → ③ 검사 창은 ±2.5kV로 좁음(벗어나면 매칭 실패). 재질이 바뀌면 시작값만 참고.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12"/>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A12:E12"/>
+  <mergeCells count="2">
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A11:E12"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/계산모델_엑셀/파라미터_계산기.xlsx
+++ b/계산모델_엑셀/파라미터_계산기.xlsx
@@ -57,7 +57,7 @@
       <color rgb="00C00000"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -89,6 +89,11 @@
         <fgColor rgb="00DDEBF7"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4D6"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="11">
     <border>
@@ -209,7 +214,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -261,6 +266,8 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -626,7 +633,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:E41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -649,7 +656,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="22" t="inlineStr">
         <is>
@@ -660,7 +666,6 @@
       <c r="C4" s="23" t="n"/>
       <c r="D4" s="23" t="n"/>
     </row>
-    <row r="5"/>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
@@ -918,8 +923,177 @@
         </is>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" s="39" t="inlineStr">
+        <is>
+          <t>■ 한 번에 검사되는 범프 수 / shot 수</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>사용할 R</t>
+        </is>
+      </c>
+      <c r="B28" s="28">
+        <f>B14</f>
+        <v/>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>µm/px</t>
+        </is>
+      </c>
+      <c r="D28" s="27" t="inlineStr">
+        <is>
+          <t>보통 R_max 사용(품질 한도 내 가장 거칠어 가장 빠름)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>검사할 범프 수(목표)</t>
+        </is>
+      </c>
+      <c r="B29" s="25" t="n">
+        <v>300</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>개</t>
+        </is>
+      </c>
+      <c r="D29" s="27" t="inlineStr">
+        <is>
+          <t>이번 검사에서 커버할 범프 수</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>범프 pitch</t>
+        </is>
+      </c>
+      <c r="B30" s="25" t="n">
+        <v>100</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>µm</t>
+        </is>
+      </c>
+      <c r="D30" s="27" t="inlineStr">
+        <is>
+          <t>도면값(범프 간격)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>[기준] R0.2·pitch100 shot당 범프</t>
+        </is>
+      </c>
+      <c r="B31" s="25" t="n">
+        <v>50</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>개</t>
+        </is>
+      </c>
+      <c r="D31" s="27" t="inlineStr">
+        <is>
+          <t>★장비 실측으로 보정하는 기준점(예: R0.2에서 한 번에 50개)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>shot당 범프 수 @사용R</t>
+        </is>
+      </c>
+      <c r="B32" s="28">
+        <f>ROUND(B31*(B28/0.2)^2*(100/B30)^2,0)</f>
+        <v/>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>개</t>
+        </is>
+      </c>
+      <c r="D32" s="27" t="inlineStr">
+        <is>
+          <t>FOV 면적 ∝ R² → shot당 범프 수는 R²에 비례(pitch²에 반비례)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>필요한 shot 수</t>
+        </is>
+      </c>
+      <c r="B33" s="28">
+        <f>ROUNDUP(B29/B32,0)</f>
+        <v/>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>회</t>
+        </is>
+      </c>
+      <c r="D33" s="27" t="inlineStr">
+        <is>
+          <t>목표 범프를 이만큼 나눠 촬영(타일). 검사시간 ∝ shot 수</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>최소 권장 범프 수</t>
+        </is>
+      </c>
+      <c r="B34" s="28" t="n">
+        <v>50</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>개</t>
+        </is>
+      </c>
+      <c r="D34" s="27" t="inlineStr">
+        <is>
+          <t>void% 통계·매칭률의 최소 표본. 실험은 같은 범프를 R별로 추적해 짝지어 비교</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="40" t="inlineStr">
+        <is>
+          <t>■ shot 여러 번 vs 1번 — 일관성 주의</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="27" t="inlineStr">
+        <is>
+          <t>R을 작게 하면 FOV가 좁아져 같은 범프를 여러 shot으로 나눠 찍어야 한다. 6 shot@R0.2 와 1 shot@R1 을 그대로 비교하면 ①범프가 타일 경계에서 잘림 ②콘빔 특성상 FOV 가장자리 범프는 비스듬히 찍혀 다르게 측정 ③스티칭 오차 로 일관성이 깨질 수 있다. → 해결: '가장 작은 R(0.2)에서도 1 shot에 들어오는 중앙 ~50개 범프'만 추적하면 모든 R이 1 shot=동일 범프가 되어 교란이 사라진다. 타일이 불가피하면 타일을 범프 격자에 맞추고 1 pitch 이상 겹치며, '같은 R에서 1 shot vs 타일'을 1회 대조 실험으로 검증할 것.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38"/>
+    <row r="39"/>
+    <row r="40"/>
+    <row r="41"/>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
+    <mergeCell ref="A37:E41"/>
     <mergeCell ref="A20:E22"/>
     <mergeCell ref="A25:E25"/>
   </mergeCells>
@@ -961,7 +1135,6 @@
       <c r="D2" s="20" t="n"/>
       <c r="E2" s="21" t="n"/>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="22" t="inlineStr">
         <is>

--- a/계산모델_엑셀/파라미터_계산기.xlsx
+++ b/계산모델_엑셀/파라미터_계산기.xlsx
@@ -214,7 +214,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -268,6 +268,11 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -972,33 +977,34 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>범프 pitch</t>
+      <c r="A30" s="41" t="inlineStr">
+        <is>
+          <t>[기준] R0.2 shot당 범프 수</t>
         </is>
       </c>
       <c r="B30" s="25" t="n">
-        <v>100</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>µm</t>
+        <v>50</v>
+      </c>
+      <c r="C30" s="42" t="inlineStr">
+        <is>
+          <t>개(미확정)</t>
         </is>
       </c>
       <c r="D30" s="27" t="inlineStr">
         <is>
-          <t>도면값(범프 간격)</t>
+          <t>※ 아직 장비 실측값이 아닌 예시 추정치입니다. 실제 R0.2 화면에서 shot당 범프 수를 세어 이 칸에 넣으면 아래 계산이 전부 정확해집니다. (pitch 보정항은 제외 — 검사 성공률에 대한 영향이 작다고 판단되어 뺌)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>[기준] R0.2·pitch100 shot당 범프</t>
-        </is>
-      </c>
-      <c r="B31" s="25" t="n">
-        <v>50</v>
+          <t>shot당 범프 수 @사용R</t>
+        </is>
+      </c>
+      <c r="B31" s="28">
+        <f>ROUND(B30*(B28/0.2)^2,0)</f>
+        <v/>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -1007,93 +1013,76 @@
       </c>
       <c r="D31" s="27" t="inlineStr">
         <is>
-          <t>★장비 실측으로 보정하는 기준점(예: R0.2에서 한 번에 50개)</t>
+          <t>FOV 면적 ∝ R² 만 반영(픽셀수 고정 가정). pitch차이는 미반영</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>shot당 범프 수 @사용R</t>
+          <t>필요한 shot 수</t>
         </is>
       </c>
       <c r="B32" s="28">
-        <f>ROUND(B31*(B28/0.2)^2*(100/B30)^2,0)</f>
+        <f>ROUNDUP(B29/B31,0)</f>
         <v/>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>개</t>
+          <t>회</t>
         </is>
       </c>
       <c r="D32" s="27" t="inlineStr">
         <is>
-          <t>FOV 면적 ∝ R² → shot당 범프 수는 R²에 비례(pitch²에 반비례)</t>
+          <t>목표 범프를 이만큼 나눠 촬영(타일). 검사시간 ∝ shot 수</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>필요한 shot 수</t>
-        </is>
-      </c>
-      <c r="B33" s="28">
-        <f>ROUNDUP(B29/B32,0)</f>
-        <v/>
+          <t>최소 권장 범프 수</t>
+        </is>
+      </c>
+      <c r="B33" s="28" t="n">
+        <v>50</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>회</t>
+          <t>개</t>
         </is>
       </c>
       <c r="D33" s="27" t="inlineStr">
         <is>
-          <t>목표 범프를 이만큼 나눠 촬영(타일). 검사시간 ∝ shot 수</t>
+          <t>void% 통계·매칭률의 최소 표본. 실험은 같은 범프를 R별로 추적해 짝지어 비교</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>최소 권장 범프 수</t>
-        </is>
-      </c>
-      <c r="B34" s="28" t="n">
-        <v>50</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>개</t>
-        </is>
-      </c>
-      <c r="D34" s="27" t="inlineStr">
-        <is>
-          <t>void% 통계·매칭률의 최소 표본. 실험은 같은 범프를 R별로 추적해 짝지어 비교</t>
+      <c r="D34" s="27" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="40" t="inlineStr">
+        <is>
+          <t>■ shot 여러 번 vs 1번 — 일관성 주의</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="40" t="inlineStr">
-        <is>
-          <t>■ shot 여러 번 vs 1번 — 일관성 주의</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="27" t="inlineStr">
+      <c r="A36" s="43" t="inlineStr">
         <is>
           <t>R을 작게 하면 FOV가 좁아져 같은 범프를 여러 shot으로 나눠 찍어야 한다. 6 shot@R0.2 와 1 shot@R1 을 그대로 비교하면 ①범프가 타일 경계에서 잘림 ②콘빔 특성상 FOV 가장자리 범프는 비스듬히 찍혀 다르게 측정 ③스티칭 오차 로 일관성이 깨질 수 있다. → 해결: '가장 작은 R(0.2)에서도 1 shot에 들어오는 중앙 ~50개 범프'만 추적하면 모든 R이 1 shot=동일 범프가 되어 교란이 사라진다. 타일이 불가피하면 타일을 범프 격자에 맞추고 1 pitch 이상 겹치며, '같은 R에서 1 shot vs 타일'을 1회 대조 실험으로 검증할 것.</t>
         </is>
       </c>
     </row>
+    <row r="37"/>
     <row r="38"/>
     <row r="39"/>
     <row r="40"/>
     <row r="41"/>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A37:E41"/>
+    <mergeCell ref="A36:E40"/>
     <mergeCell ref="A20:E22"/>
     <mergeCell ref="A25:E25"/>
   </mergeCells>

--- a/계산모델_엑셀/파라미터_계산기.xlsx
+++ b/계산모델_엑셀/파라미터_계산기.xlsx
@@ -638,7 +638,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E41"/>
+  <dimension ref="A1:E40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -879,7 +879,7 @@
       <c r="C17" s="6" t="n"/>
       <c r="D17" s="24" t="inlineStr">
         <is>
-          <t>반복(재현성)이 허용되는 최소 F. 어두우면 ↑ (64→32 = 시간 절반)</t>
+          <t>반복(재현성)이 허용되는 최소 F. 어두우면 ↑ (64→32 = 시간 절반) · 장비 최소=32(그 이하 불가)</t>
         </is>
       </c>
     </row>
@@ -1079,7 +1079,6 @@
     <row r="38"/>
     <row r="39"/>
     <row r="40"/>
-    <row r="41"/>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A36:E40"/>

--- a/계산모델_엑셀/파라미터_계산기.xlsx
+++ b/계산모델_엑셀/파라미터_계산기.xlsx
@@ -732,7 +732,7 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>허용 void% 상대오차 ε</t>
+          <t>허용 총오차 ε (정확도)</t>
         </is>
       </c>
       <c r="B9" s="25" t="n">
@@ -741,7 +741,7 @@
       <c r="C9" s="6" t="n"/>
       <c r="D9" s="24" t="inlineStr">
         <is>
-          <t>0.10 = ±10%. 작을수록 N이 커짐(더 정밀·더 느림)</t>
+          <t>0.10=총오차 10%(픽셀화+노이즈). 작을수록 N↑(정밀·느림). 정확도 하드 제약</t>
         </is>
       </c>
     </row>
@@ -768,7 +768,7 @@
         </is>
       </c>
       <c r="B12" s="26">
-        <f>ROUND(2/B9,0)</f>
+        <f>ROUND(2*SQRT(2)/B9,0)</f>
         <v/>
       </c>
       <c r="C12" t="inlineStr">
@@ -778,7 +778,7 @@
       </c>
       <c r="D12" s="27" t="inlineStr">
         <is>
-          <t>N≈2/ε. void 면적을 픽셀로 쪼갤 때 생기는 오차 기준. 단순 검출만이면 ~5</t>
+          <t>정확도=총오차 ε. 픽셀화·노이즈 균등분할 → N=2√2/ε (ε10%→N≈28~29). 노이즈(σ)는 Frame으로 별도 확보</t>
         </is>
       </c>
     </row>
